--- a/important_mails_2026-06-27.xlsx
+++ b/important_mails_2026-06-27.xlsx
@@ -2031,7 +2031,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2046,71 +2046,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Sat, 20 Jun 2026 13:23:55 +0000</t>
+          <t>Wed, 24 Jun 2026 04:08:32 +0000</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Tu pago está en camino</t>
+          <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
+ B0DD7R3PPG</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 06/20/26 13:23 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 216,97.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 24 Jun 2026 04:08:32 +0000</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
- B0DD7R3PPG</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -2122,40 +2073,40 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 02:52:15 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -2174,39 +2125,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:40:10 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2221,39 +2172,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:07:09 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -2281,39 +2232,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 22:31:41 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para julio</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para julio
@@ -2342,39 +2293,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:42 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Łącze do zaktualizowanego raportu podatkowego dotyczącego Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Ponownie przesyłamy kwartalny raport podatkowy, który obejmuje dane takie jak informacje o tożsamości, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -2392,39 +2343,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 10:01:00 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2443,39 +2394,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:26 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -2489,39 +2440,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 00:26:49 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;
@@ -2536,39 +2487,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 09:29:52 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Prime会员日明天开始：最后提报促销活动的机会</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -2592,39 +2543,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sun, 21 Jun 2026 12:49:43 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2639,92 +2590,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 10:18:43 +0000</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Dein Einkaufswagen wartet</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
- -3 % 27,95 € UVP: 28,95 €
-https://www.amazon.de/gp/product/B0DRCF83VZ/?ref_=
-Einkaufswagen anzeigen
-https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schaue dir weitere Optionen an
-75x120 cm Feuerfeste Unterlage, Hitzeschutzmatte, Antihaft-Material Bodenschutzmatte, Grill Matten, Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
- 19,99 €
-https://www.amazon.de/gp/product/B0DBLM41YS/?ref_=ci_mcx_mr_2p_0_lm
-Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 982 ℃ Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
- -8 % 23,95 € UVP: 25,95 €
-https://www.amazon.de/gp/product/B0DRC8LPGS/?ref_=ci_mcx_mr_2p_1_lm
-Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
-Befristetes Angebot -18 % 20,38 € UVP: 24,95 €
-h</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 12:14:25 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Connect with an Amazon expert at Seller Café—Save $100 with early-bird pricing</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z46y96/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/4uHYwMZ-ld-EM/7z46y99/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
@@ -2740,39 +2638,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 04:41:46 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2788,39 +2686,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 14:16:06 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2841,39 +2739,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:10:33 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Multchannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -2887,39 +2785,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 20:47:57 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (oWLDk2Qx2d)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2944,39 +2842,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 20:39:11 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Emm3dPMsXA)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3001,39 +2899,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 17:59:35 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai EU,
@@ -3047,39 +2945,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 15:48:24 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3100,39 +2998,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 16:22:55 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3153,39 +3051,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 15:05:28 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3206,39 +3104,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 14:33:45 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $94.16 in an attempt to settle your Amazon seller account balance.
@@ -3254,39 +3152,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 21:11:17 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3307,39 +3205,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 03:06:46 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3355,39 +3253,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 16:09:43 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (JKfyD/ypoS)</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3407,39 +3305,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 04:19:55 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (wrlLFrQcT3)</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3459,39 +3357,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 18:59:47 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2605311NRC)</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3511,39 +3409,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 16:46:32 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3564,39 +3462,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 03:33:45 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3612,39 +3510,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 05:07:33 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (MtDohxu3JK)</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3664,39 +3562,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 13:57:10 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (okvedC6bat)</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3716,39 +3614,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 08:40:44 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3764,39 +3662,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 19:29:32 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (260520getf)</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3821,39 +3719,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:43:35 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $143.78 in an attempt to settle your Amazon seller account balance.
@@ -3869,39 +3767,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 01:13:32 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq5h330940)</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3926,39 +3824,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 06:55:02 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7kDrHSJf1h)</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3978,39 +3876,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 03:26:42 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4026,39 +3924,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 13:57:34 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Iot4D83CtY)</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4078,39 +3976,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 14:32:29 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Seller News: June 2026</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4127,39 +4025,88 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 20 Jun 2026 13:23:55 +0000</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 06/20/26 13:23 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 216,97.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 13:11:15 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4179,39 +4126,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 13:09:47 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4228,39 +4175,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 17:21:56 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January–March 2026</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -4277,39 +4224,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 16:54:51 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -4326,39 +4273,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 08:40:50 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Envía el número de registro de España para la responsabilidad ampliada del productor con respecto a los RAEE a más tardar el 30 de septiembre</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Presenta el número de registro de la responsabilidad ampliada del productor a más tardar el 30 de septiembre o se te inscribirá automáticamente en RAP: Pago en mi nombre.
  96
@@ -4367,39 +4314,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 14:39:03 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4419,39 +4366,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:27:04 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4471,39 +4418,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:25:49 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4520,39 +4467,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:24:48 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4572,39 +4519,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 06:40:46 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Seller Central &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>重要信息：即刻重新验证您的所有 付款账户或存款方式</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  亲爱的卖家，
@@ -4638,39 +4585,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:24:03 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4690,39 +4637,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:23:28 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4739,39 +4686,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 13:35:44 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4791,39 +4738,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:28:40 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4843,39 +4790,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:24:36 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4892,39 +4839,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:24:04 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4944,39 +4891,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 23:31:42 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4996,39 +4943,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 12:54:19 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5048,39 +4995,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 15:13:12 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 42.71. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -5094,39 +5041,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:53:43 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5146,39 +5093,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 11:51:09 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5195,39 +5142,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 16:29:28 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;informacion-vendedor@amazon.mx&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Pago del saldo en tu cuenta de pagos de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Estimado vendedor:
  Hemos realizado un cargo en tu tarjeta de crédito (Visa) por valor de MXN 90.75 con el fin de saldar tu cuenta de vendedor de Amazon.
@@ -5239,39 +5186,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 02:57:49 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5291,39 +5238,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 02:56:47 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5340,39 +5287,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 02:56:35 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5392,39 +5339,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 8 Jun 2026 14:05:53 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5444,39 +5391,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 13:51:46 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5496,39 +5443,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:50 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5548,39 +5495,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sat, 6 Jun 2026 13:21:46 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5597,39 +5544,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 15:15:46 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5649,39 +5596,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5698,39 +5645,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 14:58:44 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5750,39 +5697,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:36 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5802,39 +5749,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5854,39 +5801,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 14:37:25 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5903,39 +5850,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5955,39 +5902,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:43:44 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6007,39 +5954,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:42:27 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6059,39 +6006,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 14:51:20 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -6107,39 +6054,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 12:40:58 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6155,39 +6102,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:56:40 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6213,39 +6160,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:39:22 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6271,39 +6218,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 10:15:17 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Submit EPR registration numbers by June 30</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -6312,39 +6259,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 04:34:37 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -6369,40 +6316,40 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 06:03:25 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -6420,40 +6367,40 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 19:23:07 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -6478,39 +6425,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:11:59 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -6529,39 +6476,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:32 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6580,39 +6527,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:28 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -6631,39 +6578,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:32:14 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"pars-rp-core-sellerappeals-transfer@amazon.com" &lt;pars-rp-core-sellerappeals-transfer@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20516062511] 危险物品（危险品）</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20516062511] 危险物品（危险品）
@@ -6691,39 +6638,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:13:22 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6742,39 +6689,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 20:37:03 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Important message: your account is at risk of deactivation</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  96
@@ -6794,40 +6741,40 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 06:46:26 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -6843,40 +6790,40 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 10:18:49 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -6903,39 +6850,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 03:03:53 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Review issue on FBA Shipment (FBA1234567)</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Review shipment defects to avoid reoccurrence
@@ -6955,40 +6902,40 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 13:54:53 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -7001,40 +6948,40 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 10:51:40 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -7053,39 +7000,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 13:08:16 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -7104,40 +7051,40 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 11 Jun 2026 04:06:26 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC - DOC REVIEW
@@ -7153,39 +7100,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 19:04:36 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>New EU restriction on textile and footwear disposal</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  By July 19, update your removal settings for apparel, clothing and footwear in EU fulfillment centers
@@ -7200,39 +7147,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 18:11:21 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7250,40 +7197,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 10 Jun 2026 02:29:01 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -7295,39 +7242,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 18:10:54 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7345,39 +7292,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Tue, 9 Jun 2026 15:30:18 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.es sales</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tu factura con IVA de los cargos del servicio RAP - Pagamos en tu nombre para las ventas de Amazon.es |
 Your VAT invoice for EPR Pay on Behalf charges for Amazon.es sales
@@ -7390,40 +7337,40 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Mon, 8 Jun 2026 08:56:37 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -7439,40 +7386,40 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Mon, 8 Jun 2026 08:52:27 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GKPTF1T7, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GKPTF1T7, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -7500,39 +7447,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sun, 7 Jun 2026 17:51:49 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -7551,39 +7498,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 19:25:12 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7601,39 +7548,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 03:06:03 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -7653,39 +7600,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:23:36 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7703,39 +7650,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:17:04 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7753,39 +7700,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:40:15 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -7801,39 +7748,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:33:38 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -7852,39 +7799,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 21:10:43 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7902,39 +7849,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:18:22 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7952,39 +7899,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:12:35 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8002,39 +7949,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 02:36:04 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12662433092] 通过亚马逊完成奥地利EPR注册</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12662433092] 通过亚马逊完成奥地利EPR注册
@@ -8069,39 +8016,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 12:53:21 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -8117,40 +8064,40 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 10:39:43 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.se" &lt;cscompliance-docreview-seller@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review
@@ -8167,40 +8114,40 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:31:42 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS -
  APPEAL</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS - APPEAL
@@ -8221,39 +8168,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:48 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8271,39 +8218,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:09:04 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8321,39 +8268,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:43 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8371,39 +8318,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:07:21 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8421,39 +8368,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 06:06:12 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>帮您免费一站式搞定VAT、EPR等合规问题！亚马逊合规服务商城现已正式上线！</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>亚马逊合规服务商城正式上线，一站式帮助卖家高效搞定欧洲站点的VAT、EPR等合规问题。
 			尊敬的 深圳市微海众信科技有限公司,
@@ -8483,39 +8430,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 17:40:38 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -8531,6 +8478,59 @@
 Was this email helpful?
  https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
 SPC-USAmazon-2023103611500356</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 20 Jun 2026 10:18:43 +0000</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
+ -3 % 27,95 € UVP: 28,95 €
+https://www.amazon.de/gp/product/B0DRCF83VZ/?ref_=
+Einkaufswagen anzeigen
+https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schaue dir weitere Optionen an
+75x120 cm Feuerfeste Unterlage, Hitzeschutzmatte, Antihaft-Material Bodenschutzmatte, Grill Matten, Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
+ 19,99 €
+https://www.amazon.de/gp/product/B0DBLM41YS/?ref_=ci_mcx_mr_2p_0_lm
+Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 982 ℃ Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
+ -8 % 23,95 € UVP: 25,95 €
+https://www.amazon.de/gp/product/B0DRC8LPGS/?ref_=ci_mcx_mr_2p_1_lm
+Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
+Befristetes Angebot -18 % 20,38 € UVP: 24,95 €
+h</t>
         </is>
       </c>
     </row>
